--- a/src/main/resources/static/profile.xlsx
+++ b/src/main/resources/static/profile.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\14Z90N\Desktop\coding\WorkSpace\GroupAssignerAssist\src\main\resources\static\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\14Z90N\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0A3DD4-74DD-40D8-A92F-918A449836E5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D43BAD2C-578B-41F0-8B94-E5CFD190C8C5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8856" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="조편성 결과" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -30,10 +30,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>job</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>M</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -43,14 +39,6 @@
   </si>
   <si>
     <t>김알토</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>job1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>job2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -451,40 +439,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
